--- a/EPN_facilities.xlsx
+++ b/EPN_facilities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sum223\Documents\Projects\NAVFAC-Incore\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sushreyomisra07/Documents/GitHub/FloodRiskBTP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCEB469-AEF2-464D-B5F7-2EA3733A3452}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AE81A4-4A6F-C84C-AC01-24ECFB3C9BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11385" activeTab="2" xr2:uid="{7713A25D-7047-4BE5-B59D-81615470B2F5}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="19200" windowHeight="11380" activeTab="2" xr2:uid="{7713A25D-7047-4BE5-B59D-81615470B2F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Power_Plants" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="42">
   <si>
     <t>Herbert A Wagner Generating Station</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>Nimitz Laboratory</t>
+  </si>
+  <si>
+    <t>Barrier_ht</t>
   </si>
 </sst>
 </file>
@@ -212,9 +215,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -252,7 +255,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -358,7 +361,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -500,7 +503,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -509,9 +512,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6FED44D-86D4-46E9-9B58-F887B4AA0D54}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -528,7 +531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -545,7 +548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -570,12 +573,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484B7608-B400-49F9-98B0-0A52DF03BAEC}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -595,7 +598,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3</v>
       </c>
@@ -615,7 +618,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4</v>
       </c>
@@ -635,7 +638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>5</v>
       </c>
@@ -655,7 +658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>6</v>
       </c>
@@ -675,7 +678,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>7</v>
       </c>
@@ -695,7 +698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>8</v>
       </c>
@@ -722,10 +725,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E38F69C-4A0E-3A4A-8887-27809B7BEC96}">
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -742,19 +745,22 @@
         <v>20</v>
       </c>
       <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -771,19 +777,22 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>30</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>25</v>
       </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -800,19 +809,22 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
         <v>30</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -829,19 +841,22 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>25</v>
       </c>
-      <c r="I4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -858,19 +873,22 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
         <v>30</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>25</v>
       </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -887,19 +905,22 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
         <v>30</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>25</v>
       </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -916,19 +937,22 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
         <v>30</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>25</v>
       </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -945,19 +969,22 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
         <v>30</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>25</v>
       </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -974,19 +1001,22 @@
         <v>0</v>
       </c>
       <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>3</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>40</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>33</v>
       </c>
-      <c r="I9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1003,19 +1033,22 @@
         <v>0</v>
       </c>
       <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <v>3</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>40</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>33</v>
       </c>
-      <c r="I10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1032,19 +1065,22 @@
         <v>0</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>3</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>40</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>33</v>
       </c>
-      <c r="I11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1061,19 +1097,22 @@
         <v>0</v>
       </c>
       <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <v>3</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>40</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>33</v>
       </c>
-      <c r="I12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1090,19 +1129,22 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
         <v>30</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>33</v>
       </c>
-      <c r="I13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1119,19 +1161,22 @@
         <v>0</v>
       </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>25</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>39</v>
       </c>
-      <c r="I14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1148,15 +1193,18 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
         <v>30</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>33</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>6</v>
       </c>
     </row>

--- a/EPN_facilities.xlsx
+++ b/EPN_facilities.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sushreyomisra07/Documents/GitHub/FloodRiskBTP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AE81A4-4A6F-C84C-AC01-24ECFB3C9BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142A287E-C5C9-FA48-83DD-99A5BB808882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="19200" windowHeight="11380" activeTab="2" xr2:uid="{7713A25D-7047-4BE5-B59D-81615470B2F5}"/>
+    <workbookView xWindow="1860" yWindow="500" windowWidth="26580" windowHeight="17960" activeTab="2" xr2:uid="{7713A25D-7047-4BE5-B59D-81615470B2F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Power_Plants" sheetId="1" r:id="rId1"/>

--- a/EPN_facilities.xlsx
+++ b/EPN_facilities.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sushreyomisra07/Documents/GitHub/FloodRiskBTP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142A287E-C5C9-FA48-83DD-99A5BB808882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE3B1A0-45BE-2C4E-801D-4834F2630D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="500" windowWidth="26580" windowHeight="17960" activeTab="2" xr2:uid="{7713A25D-7047-4BE5-B59D-81615470B2F5}"/>
+    <workbookView xWindow="1860" yWindow="760" windowWidth="26580" windowHeight="17900" activeTab="1" xr2:uid="{7713A25D-7047-4BE5-B59D-81615470B2F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Power_Plants" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
   <si>
     <t>Herbert A Wagner Generating Station</t>
   </si>
@@ -159,7 +159,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,6 +172,13 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -194,9 +201,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,10 +519,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6FED44D-86D4-46E9-9B58-F887B4AA0D54}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -528,10 +536,13 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -544,11 +555,14 @@
       <c r="D2">
         <v>-76.441607000000005</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -561,7 +575,10 @@
       <c r="D3">
         <v>-76.525818999999998</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -572,13 +589,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484B7608-B400-49F9-98B0-0A52DF03BAEC}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -594,11 +612,14 @@
       <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3</v>
       </c>
@@ -614,11 +635,14 @@
       <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4</v>
       </c>
@@ -635,10 +659,13 @@
         <v>15</v>
       </c>
       <c r="F3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>5</v>
       </c>
@@ -655,10 +682,13 @@
         <v>15</v>
       </c>
       <c r="F4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>6</v>
       </c>
@@ -675,10 +705,13 @@
         <v>15</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>7</v>
       </c>
@@ -695,10 +728,13 @@
         <v>15</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>8</v>
       </c>
@@ -715,6 +751,9 @@
         <v>15</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>
